--- a/submissions/Tarun2712_methods_description_form.xlsx
+++ b/submissions/Tarun2712_methods_description_form.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Anthropic Claude Code (model: Claude Opus 5.5) was used interactively to review the plan, write and debug the pipeline code, and draft this report. Plan/tier: `[TODO: fill in, e.g. Claude Pro/Max/Team]`; data-handling setting: `[TODO: e.g. "model training on my data disabled"]`. The assistant ran the pipeline locally. Panel-region variant annotations were therefore visible to the assistant during the session, but no raw reads and no whole-genome VCF content were sent to it. No patient data was sent to any external annotation service: all annotation ran locally.</t>
+          <t>Anthropic Claude Code (model: Claude Opus 5.5) was used interactively to review the plan, write and debug the pipeline code, and draft this report. Plan/tier: Claude Max subscription (consumer terms), used through the Claude Code CLI. Data handling: the session ran on the local machine; the assistant did not upload any dataset files. The assistant ran the pipeline locally. Panel-region variant annotations were therefore visible to the assistant during the session, but no raw reads and no whole-genome VCF content were sent to it. No patient data was sent to any external annotation service: all annotation ran locally.</t>
         </is>
       </c>
     </row>

--- a/submissions/Tarun2712_methods_description_form.xlsx
+++ b/submissions/Tarun2712_methods_description_form.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Anthropic Claude Code (model: Claude Opus 5.5) was used interactively to review the plan, write and debug the pipeline code, and draft this report. Plan/tier: Claude Max subscription (consumer terms), used through the Claude Code CLI. Data handling: the session ran on the local machine; the assistant did not upload any dataset files. The assistant ran the pipeline locally. Panel-region variant annotations were therefore visible to the assistant during the session, but no raw reads and no whole-genome VCF content were sent to it. No patient data was sent to any external annotation service: all annotation ran locally.</t>
+          <t>Anthropic Claude Code (models: Claude Opus 5.5 for the pipeline and report drafting; Claude Fable 5.1 for final edits) was used interactively to review the plan, write and debug the pipeline code, and draft this report. Plan/tier: Claude Max subscription (consumer terms), used through the Claude Code CLI. Data handling: the session ran on the local machine; the assistant did not upload any dataset files. The assistant ran the pipeline locally. Panel-region variant annotations were therefore visible to the assistant during the session, but no raw reads and no whole-genome VCF content were sent to it. No patient data was sent to any external annotation service: all annotation ran locally.</t>
         </is>
       </c>
     </row>

--- a/submissions/Tarun2712_methods_description_form.xlsx
+++ b/submissions/Tarun2712_methods_description_form.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Anthropic Claude Code (models: Claude Opus 5.5 for the pipeline and report drafting; Claude Fable 5.1 for final edits) was used interactively to review the plan, write and debug the pipeline code, and draft this report. Plan/tier: Claude Max subscription (consumer terms), used through the Claude Code CLI. Data handling: the session ran on the local machine; the assistant did not upload any dataset files. The assistant ran the pipeline locally. Panel-region variant annotations were therefore visible to the assistant during the session, but no raw reads and no whole-genome VCF content were sent to it. No patient data was sent to any external annotation service: all annotation ran locally.</t>
+          <t>Anthropic Claude Code (models: Claude Opus 5.5 for the pipeline and report drafting; Claude Fable 5.1 for final edits) was used interactively to review the plan, write and debug the pipeline code, and draft this report. Plan/tier: Claude Max subscription (consumer terms), used through the Claude Code CLI. Data handling: default consumer setting with "Help improve Claude" (model training) enabled; the session ran on the local machine and the assistant did not upload any dataset files. The assistant ran the pipeline locally. Panel-region variant annotations were therefore visible to the assistant during the session, but no raw reads and no whole-genome VCF content were sent to it. No patient data was sent to any external annotation service: all annotation ran locally.</t>
         </is>
       </c>
     </row>
